--- a/lab-standards/BWCCI-lab-standard.xlsx
+++ b/lab-standards/BWCCI-lab-standard.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -138,6 +138,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -562,6 +568,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -576,6 +586,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1106,7 +1120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -1238,16 +1252,16 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Computers/Laptop</t>
+          <t>Computer / Laptop (with relevant design software)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="9" t="n">
@@ -1260,12 +1274,12 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Projector &amp; Screen (HD quality, HDMI support, 3000+ lumens)</t>
+          <t>Multimedia Projector &amp; Screen (HD quality, HDMI support)</t>
         </is>
       </c>
       <c r="C17" s="9" t="n">
@@ -1282,7 +1296,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1304,20 +1318,20 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Mannequins/Dress Forms (Female and male standard sizes)</t>
+          <t>Single Needle Lock Stitch Machine (Industrial/Domestic)</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -1326,20 +1340,20 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Single needle lock stitch machine</t>
+          <t>Overlock Machine (3 or 4 threads)</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -1348,20 +1362,20 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Overlock machine</t>
+          <t>Embroidery Machine (Manual/Computerized)</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -1370,20 +1384,20 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Cutting table (60”x 50”)</t>
+          <t>Button Hole Machine</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -1392,12 +1406,12 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Electric iron</t>
+          <t>Button Stitch Machine</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
@@ -1414,20 +1428,20 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Electric steam iron with iron table</t>
+          <t>Cutting Table (Standard size: min. 5ft - 60”x50”)</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -1436,20 +1450,20 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Scissors (10”-12”)</t>
+          <t>Pattern Making &amp; Printing Table (Min 5ft)</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -1458,20 +1472,20 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Sewing tool box</t>
+          <t>Mannequins / Dress Forms (Male, Female, and Child standard sizes)</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -1479,57 +1493,233 @@
       </c>
       <c r="G26" s="9" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="27" ht="14.15" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Electric Steam Iron with Ironing Table</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" s="9">
+        <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="14.15" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Burner for Dyeing and Printing</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="9">
+        <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="9" t="n"/>
+    </row>
+    <row r="29" ht="14.15" customHeight="1">
+      <c r="A29" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Tracing Wheels</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="9">
+        <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="14.15" customHeight="1">
+      <c r="A30" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Sets of Pattern Making Curves (French curve, Hip curve, etc.)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="9">
+        <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="14.15" customHeight="1">
+      <c r="A31" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Fabric Cutting Scissors (10”-12”)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="9">
+        <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="14.15" customHeight="1">
+      <c r="A32" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Different Screen for Printing</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="9">
+        <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="9" t="n"/>
+    </row>
+    <row r="33" ht="14.15" customHeight="1">
+      <c r="A33" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Different Dices for Block Printing</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="9">
+        <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="9" t="n"/>
+    </row>
+    <row r="34" ht="14.15" customHeight="1">
+      <c r="A34" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Sewing Tool Box (Measuring tape, tailor’s chalk, needles, etc.)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="9">
+        <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="10">
-        <f>SUM(E16:E26)</f>
-        <v/>
-      </c>
-      <c r="F27" s="10">
-        <f>SUM(F16:F26)</f>
-        <v/>
-      </c>
-      <c r="G27" s="13" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="15">
+        <f>SUM(E16:E34)</f>
+        <v/>
+      </c>
+      <c r="F35" s="15">
+        <f>SUM(F16:F34)</f>
+        <v/>
+      </c>
+      <c r="G35" s="13" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="10">
-        <f>F27/E27*100</f>
-        <v/>
-      </c>
-      <c r="G28" s="13" t="n"/>
-    </row>
-    <row r="29" ht="9.75" customHeight="1"/>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="15">
+        <f>F35/E35*100</f>
+        <v/>
+      </c>
+      <c r="G36" s="13" t="n"/>
+    </row>
+    <row r="37" ht="9.75" customHeight="1"/>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
       </c>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="10">
-        <f>F28*30/100</f>
-        <v/>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="15">
+        <f>F36*30/100</f>
+        <v/>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1537,14 +1727,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A30:E30"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A36:E36"/>
     <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1615,6 +1805,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1628,6 +1822,10 @@
 Workshop/ lab – 800 sft (75 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2239,6 +2437,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2254,6 +2456,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2623,6 +2829,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2635,6 +2845,10 @@
           <t>Classroom cum workshop – 500 - 600 sft (50-55 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3026,6 +3240,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3040,6 +3258,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3629,6 +3851,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3644,6 +3870,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">

--- a/lab-standards/BWCCI-lab-standard.xlsx
+++ b/lab-standards/BWCCI-lab-standard.xlsx
@@ -648,7 +648,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -659,7 +659,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -670,7 +672,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -681,7 +683,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -692,7 +696,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -703,7 +707,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -714,7 +720,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -725,7 +731,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -736,7 +744,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -747,7 +755,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -758,7 +768,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -769,7 +779,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -780,7 +792,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -791,7 +803,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -802,7 +816,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -813,7 +827,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -824,7 +840,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -835,7 +851,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -846,7 +864,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -857,7 +875,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>8</v>
       </c>
@@ -868,7 +888,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -879,7 +899,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -890,7 +912,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -901,7 +923,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -912,7 +936,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -923,7 +947,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -934,7 +960,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -945,7 +971,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -956,7 +984,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -967,7 +995,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -978,7 +1008,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -989,7 +1019,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>9</v>
       </c>
@@ -1000,7 +1032,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1011,7 +1043,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -1022,7 +1056,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1033,7 +1067,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -1044,7 +1080,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1052,18 +1088,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="10">
+      <c r="E34" s="15">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="15">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1072,7 +1108,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -1080,7 +1116,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1089,11 +1125,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="10">
+      <c r="F37" s="15">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1179,6 +1215,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1194,6 +1234,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1263,7 +1307,9 @@
       <c r="C16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1285,7 +1331,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1307,7 +1355,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -1329,7 +1379,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -1351,7 +1403,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -1373,7 +1427,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -1395,7 +1451,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -1417,7 +1475,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -1439,7 +1499,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -1461,7 +1523,9 @@
       <c r="C25" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -1483,7 +1547,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>9</v>
       </c>
@@ -1505,7 +1571,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -1527,7 +1595,9 @@
       <c r="C28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -1549,7 +1619,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -1571,7 +1643,9 @@
       <c r="C30" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -1593,7 +1667,9 @@
       <c r="C31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -1615,7 +1691,9 @@
       <c r="C32" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -1637,7 +1715,9 @@
       <c r="C33" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -1659,7 +1739,9 @@
       <c r="C34" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -1884,7 +1966,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1895,7 +1977,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1906,7 +1990,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1917,7 +2001,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1928,7 +2014,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1939,7 +2025,9 @@
       <c r="C18" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -1950,7 +2038,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1961,7 +2049,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -1972,7 +2062,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1983,7 +2073,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -1994,7 +2086,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2005,7 +2097,9 @@
       <c r="C21" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -2016,7 +2110,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2027,7 +2121,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -2038,7 +2134,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2049,7 +2145,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -2060,7 +2158,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2071,7 +2169,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -2082,7 +2182,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2093,7 +2193,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -2104,7 +2206,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2115,7 +2217,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -2126,7 +2230,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2137,7 +2241,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>9</v>
       </c>
@@ -2148,7 +2254,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2159,7 +2265,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>7</v>
       </c>
@@ -2170,7 +2278,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -2181,7 +2289,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -2192,7 +2302,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -2203,7 +2313,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>5</v>
       </c>
@@ -2214,7 +2326,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -2225,7 +2337,9 @@
       <c r="C31" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -2236,7 +2350,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -2247,7 +2361,9 @@
       <c r="C32" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>4</v>
       </c>
@@ -2258,7 +2374,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2269,7 +2385,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>4</v>
       </c>
@@ -2280,7 +2398,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -2291,7 +2409,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -2302,7 +2422,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2310,18 +2430,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="10">
+      <c r="E35" s="15">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2330,7 +2450,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -2338,7 +2458,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2347,11 +2467,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -2518,7 +2638,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2529,7 +2649,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -2540,7 +2662,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2551,7 +2673,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -2562,7 +2686,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2573,7 +2697,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -2584,7 +2710,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2595,7 +2721,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -2606,7 +2734,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2617,7 +2745,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -2628,7 +2758,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2639,7 +2769,9 @@
       <c r="C21" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -2650,7 +2782,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2661,7 +2793,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -2672,7 +2806,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2683,7 +2817,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -2694,7 +2830,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2702,18 +2838,18 @@
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12" t="n"/>
-      <c r="E24" s="10">
+      <c r="E24" s="15">
         <f>SUM(E16:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="15">
         <f>SUM(F16:F23)</f>
         <v/>
       </c>
       <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2722,7 +2858,7 @@
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="12" t="n"/>
-      <c r="F25" s="10">
+      <c r="F25" s="15">
         <f>F24/E24*100</f>
         <v/>
       </c>
@@ -2730,7 +2866,7 @@
     </row>
     <row r="26" ht="9.75" customHeight="1"/>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2739,11 +2875,11 @@
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="12" t="n"/>
-      <c r="F27" s="10">
+      <c r="F27" s="15">
         <f>F25*30/100</f>
         <v/>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -2907,7 +3043,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2918,7 +3054,9 @@
       <c r="C16" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -2929,7 +3067,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2940,7 +3078,9 @@
       <c r="C17" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -2951,7 +3091,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2962,7 +3102,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -2973,7 +3115,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2984,7 +3126,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -2995,7 +3139,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3006,7 +3150,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -3017,7 +3163,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3028,7 +3174,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -3039,7 +3187,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3050,7 +3198,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -3061,7 +3211,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -3072,7 +3222,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -3083,7 +3235,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -3094,7 +3246,9 @@
       <c r="C24" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -3105,7 +3259,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3113,18 +3267,18 @@
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="10">
+      <c r="E25" s="15">
         <f>SUM(E16:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="15">
         <f>SUM(F16:F24)</f>
         <v/>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3133,7 +3287,7 @@
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="12" t="n"/>
-      <c r="F26" s="10">
+      <c r="F26" s="15">
         <f>F25/E25*100</f>
         <v/>
       </c>
@@ -3141,7 +3295,7 @@
     </row>
     <row r="27" ht="9.75" customHeight="1"/>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3150,11 +3304,11 @@
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="11" t="n"/>
       <c r="E28" s="12" t="n"/>
-      <c r="F28" s="10">
+      <c r="F28" s="15">
         <f>F26*30/100</f>
         <v/>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -3320,7 +3474,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -3331,7 +3485,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -3342,7 +3498,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3353,7 +3509,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -3364,7 +3522,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3375,7 +3533,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -3386,7 +3546,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3397,7 +3557,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -3408,7 +3570,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3419,7 +3581,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -3430,7 +3594,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3441,7 +3605,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -3452,7 +3618,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3463,7 +3629,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -3474,7 +3642,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -3485,7 +3653,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -3496,7 +3666,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -3507,7 +3677,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -3518,7 +3690,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -3529,7 +3701,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>8</v>
       </c>
@@ -3540,7 +3714,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -3551,7 +3725,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -3562,7 +3738,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -3573,7 +3749,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -3584,7 +3762,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -3595,7 +3773,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -3606,7 +3786,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -3617,7 +3797,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -3628,7 +3810,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -3639,7 +3821,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -3650,7 +3834,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -3661,7 +3845,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>9</v>
       </c>
@@ -3672,7 +3858,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -3683,7 +3869,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -3694,7 +3882,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3705,7 +3893,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -3716,7 +3906,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3724,18 +3914,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="10">
+      <c r="E34" s="15">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="15">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3744,7 +3934,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -3752,7 +3942,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3761,11 +3951,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="10">
+      <c r="F37" s="15">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -3932,7 +4122,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -3943,7 +4133,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -3954,7 +4146,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3965,7 +4157,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -3976,7 +4170,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3987,7 +4181,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -3998,7 +4194,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -4009,7 +4205,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -4020,7 +4218,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -4031,7 +4229,9 @@
       <c r="C20" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>10</v>
       </c>
@@ -4042,7 +4242,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -4053,7 +4253,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -4064,7 +4266,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -4075,7 +4277,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -4086,7 +4290,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -4097,7 +4301,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -4108,7 +4314,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -4119,7 +4325,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -4130,7 +4338,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -4141,7 +4349,9 @@
       <c r="C25" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -4152,7 +4362,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -4163,7 +4373,9 @@
       <c r="C26" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -4174,7 +4386,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -4182,18 +4394,18 @@
       <c r="B27" s="11" t="n"/>
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="12" t="n"/>
-      <c r="E27" s="10">
+      <c r="E27" s="15">
         <f>SUM(E16:E26)</f>
         <v/>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="15">
         <f>SUM(F16:F26)</f>
         <v/>
       </c>
       <c r="G27" s="13" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -4202,7 +4414,7 @@
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="11" t="n"/>
       <c r="E28" s="12" t="n"/>
-      <c r="F28" s="10">
+      <c r="F28" s="15">
         <f>F27/E27*100</f>
         <v/>
       </c>
@@ -4210,7 +4422,7 @@
     </row>
     <row r="29" ht="9.75" customHeight="1"/>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -4219,11 +4431,11 @@
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="12" t="n"/>
-      <c r="F30" s="10">
+      <c r="F30" s="15">
         <f>F28*30/100</f>
         <v/>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>

--- a/lab-standards/BWCCI-lab-standard.xlsx
+++ b/lab-standards/BWCCI-lab-standard.xlsx
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Weighing Scale (Preferred capacity mm)</t>
+          <t>Weighing Scale (Preferred capacity 10 kg)</t>
         </is>
       </c>
       <c r="C33" s="9" t="n">

--- a/lab-standards/BWCCI-lab-standard.xlsx
+++ b/lab-standards/BWCCI-lab-standard.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -138,6 +138,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3982,7 +3988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -4041,10 +4047,6 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -4060,10 +4062,6 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4122,16 +4120,16 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Computers/Laptop</t>
+          <t>Computer / Laptop (with relevant design software)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>0</v>
@@ -4146,12 +4144,12 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Projector &amp; Screen (HD quality, HDMI support, 3000+ lumens)</t>
+          <t>Multimedia Projector &amp; Screen (HD quality, HDMI support)</t>
         </is>
       </c>
       <c r="C17" s="9" t="n">
@@ -4170,7 +4168,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -4194,22 +4192,22 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Mannequins/Dress Forms (Female and male standard sizes)</t>
+          <t>Single Needle Lock Stitch Machine (Industrial/Domestic)</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -4218,22 +4216,22 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Single needle lock stitch machine</t>
+          <t>Overlock Machine (3 or 4 threads)</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -4242,22 +4240,22 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Overlock machine</t>
+          <t>Embroidery Machine (Manual/Computerized)</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -4266,22 +4264,22 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Cutting table (60”x 50”)</t>
+          <t>Button Hole Machine</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -4290,12 +4288,12 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Electric iron</t>
+          <t>Button Stitch Machine</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
@@ -4314,22 +4312,22 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Electric steam iron with iron table</t>
+          <t>Cutting Table (Standard size: min. 5ft - 60”x50”)</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -4338,22 +4336,22 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Scissors (10”-12”)</t>
+          <t>Pattern Making &amp; Printing Table (Min 5ft)</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -4362,22 +4360,22 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Sewing tool box</t>
+          <t>Mannequins / Dress Forms (Male, Female, and Child standard sizes)</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -4385,57 +4383,249 @@
       </c>
       <c r="G26" s="9" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+    <row r="27" ht="14.15" customHeight="1">
+      <c r="A27" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Electric Steam Iron with Ironing Table</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" s="9">
+        <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="14.15" customHeight="1">
+      <c r="A28" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Burner for Dyeing and Printing</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="9">
+        <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="9" t="n"/>
+    </row>
+    <row r="29" ht="14.15" customHeight="1">
+      <c r="A29" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Tracing Wheels</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="9">
+        <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="14.15" customHeight="1">
+      <c r="A30" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Sets of Pattern Making Curves (French curve, Hip curve, etc.)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="9">
+        <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="14.15" customHeight="1">
+      <c r="A31" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Fabric Cutting Scissors (10”-12”)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="9">
+        <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="14.15" customHeight="1">
+      <c r="A32" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Different Screen for Printing</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="9">
+        <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="9" t="n"/>
+    </row>
+    <row r="33" ht="14.15" customHeight="1">
+      <c r="A33" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Different Dices for Block Printing</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="9">
+        <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="9" t="n"/>
+    </row>
+    <row r="34" ht="14.15" customHeight="1">
+      <c r="A34" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Sewing Tool Box (Measuring tape, tailor’s chalk, needles, etc.)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="9">
+        <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="15">
-        <f>SUM(E16:E26)</f>
-        <v/>
-      </c>
-      <c r="F27" s="15">
-        <f>SUM(F16:F26)</f>
-        <v/>
-      </c>
-      <c r="G27" s="13" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="17">
+        <f>SUM(E16:E34)</f>
+        <v/>
+      </c>
+      <c r="F35" s="17">
+        <f>SUM(F16:F34)</f>
+        <v/>
+      </c>
+      <c r="G35" s="13" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="15">
-        <f>F27/E27*100</f>
-        <v/>
-      </c>
-      <c r="G28" s="13" t="n"/>
-    </row>
-    <row r="29" ht="9.75" customHeight="1"/>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="17">
+        <f>F35/E35*100</f>
+        <v/>
+      </c>
+      <c r="G36" s="13" t="n"/>
+    </row>
+    <row r="37" ht="9.75" customHeight="1"/>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
       </c>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="15">
-        <f>F28*30/100</f>
-        <v/>
-      </c>
-      <c r="G30" s="15" t="inlineStr">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="17">
+        <f>F36*30/100</f>
+        <v/>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -4443,14 +4633,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A30:E30"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A36:E36"/>
     <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
